--- a/templates/interlocking_program.xlsx
+++ b/templates/interlocking_program.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daluis\Desktop\ZIRCON\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84527405-9FC9-4B7A-BF4F-E33C6B1D3A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABC13DD2-4F61-4619-93D1-7766EBA6268E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="841" xr2:uid="{DA8A0B08-56B9-4064-A2C2-7750A28C1876}"/>
   </bookViews>
@@ -4429,6 +4429,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="J3:K4"/>
+    <mergeCell ref="L3:M4"/>
+    <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="R3:R5"/>
+    <mergeCell ref="S3:S5"/>
     <mergeCell ref="W4:Y4"/>
     <mergeCell ref="T3:Y3"/>
     <mergeCell ref="A4:A5"/>
@@ -4445,11 +4450,6 @@
     <mergeCell ref="J2:Q2"/>
     <mergeCell ref="R2:Y2"/>
     <mergeCell ref="Z2:AA4"/>
-    <mergeCell ref="J3:K4"/>
-    <mergeCell ref="L3:M4"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="R3:R5"/>
-    <mergeCell ref="S3:S5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7604,6 +7604,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="J3:K4"/>
+    <mergeCell ref="L3:M4"/>
+    <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="R3:R5"/>
+    <mergeCell ref="S3:S5"/>
     <mergeCell ref="W4:Y4"/>
     <mergeCell ref="T3:Y3"/>
     <mergeCell ref="A4:A5"/>
@@ -7620,11 +7625,6 @@
     <mergeCell ref="J2:Q2"/>
     <mergeCell ref="R2:Y2"/>
     <mergeCell ref="Z2:AA4"/>
-    <mergeCell ref="J3:K4"/>
-    <mergeCell ref="L3:M4"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="R3:R5"/>
-    <mergeCell ref="S3:S5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10779,6 +10779,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="J3:K4"/>
+    <mergeCell ref="L3:M4"/>
+    <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="R3:R5"/>
+    <mergeCell ref="S3:S5"/>
     <mergeCell ref="W4:Y4"/>
     <mergeCell ref="T3:Y3"/>
     <mergeCell ref="A4:A5"/>
@@ -10795,11 +10800,6 @@
     <mergeCell ref="J2:Q2"/>
     <mergeCell ref="R2:Y2"/>
     <mergeCell ref="Z2:AA4"/>
-    <mergeCell ref="J3:K4"/>
-    <mergeCell ref="L3:M4"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="R3:R5"/>
-    <mergeCell ref="S3:S5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13954,6 +13954,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="J3:K4"/>
+    <mergeCell ref="L3:M4"/>
+    <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="R3:R5"/>
+    <mergeCell ref="S3:S5"/>
     <mergeCell ref="W4:Y4"/>
     <mergeCell ref="T3:Y3"/>
     <mergeCell ref="A4:A5"/>
@@ -13970,11 +13975,6 @@
     <mergeCell ref="J2:Q2"/>
     <mergeCell ref="R2:Y2"/>
     <mergeCell ref="Z2:AA4"/>
-    <mergeCell ref="J3:K4"/>
-    <mergeCell ref="L3:M4"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="R3:R5"/>
-    <mergeCell ref="S3:S5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -17129,6 +17129,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="J3:K4"/>
+    <mergeCell ref="L3:M4"/>
+    <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="R3:R5"/>
+    <mergeCell ref="S3:S5"/>
     <mergeCell ref="W4:Y4"/>
     <mergeCell ref="T3:Y3"/>
     <mergeCell ref="A4:A5"/>
@@ -17145,11 +17150,6 @@
     <mergeCell ref="J2:Q2"/>
     <mergeCell ref="R2:Y2"/>
     <mergeCell ref="Z2:AA4"/>
-    <mergeCell ref="J3:K4"/>
-    <mergeCell ref="L3:M4"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="R3:R5"/>
-    <mergeCell ref="S3:S5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -20304,6 +20304,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="J3:K4"/>
+    <mergeCell ref="L3:M4"/>
+    <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="R3:R5"/>
+    <mergeCell ref="S3:S5"/>
     <mergeCell ref="W4:Y4"/>
     <mergeCell ref="T3:Y3"/>
     <mergeCell ref="A4:A5"/>
@@ -20320,11 +20325,6 @@
     <mergeCell ref="J2:Q2"/>
     <mergeCell ref="R2:Y2"/>
     <mergeCell ref="Z2:AA4"/>
-    <mergeCell ref="J3:K4"/>
-    <mergeCell ref="L3:M4"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="R3:R5"/>
-    <mergeCell ref="S3:S5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/templates/interlocking_program.xlsx
+++ b/templates/interlocking_program.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daluis\Desktop\ZIRCON\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daluis\Desktop\ZIRCON\Repository\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABC13DD2-4F61-4619-93D1-7766EBA6268E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A46E2D41-BB33-4E55-A5E5-E7C859ABB702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="841" xr2:uid="{DA8A0B08-56B9-4064-A2C2-7750A28C1876}"/>
   </bookViews>
@@ -127,9 +127,6 @@
     <t>Layout Geometry</t>
   </si>
   <si>
-    <t>Parameters</t>
-  </si>
-  <si>
     <t>Location</t>
   </si>
   <si>
@@ -140,6 +137,9 @@
   </si>
   <si>
     <t>Auxiliary Data</t>
+  </si>
+  <si>
+    <t>Operational Parameters</t>
   </si>
 </sst>
 </file>
@@ -1460,13 +1460,13 @@
         <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F5" s="52"/>
       <c r="G5" s="2" t="s">
@@ -4635,13 +4635,13 @@
         <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F5" s="52"/>
       <c r="G5" s="2" t="s">
@@ -7810,13 +7810,13 @@
         <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F5" s="52"/>
       <c r="G5" s="2" t="s">
@@ -10985,13 +10985,13 @@
         <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F5" s="52"/>
       <c r="G5" s="2" t="s">
@@ -14160,13 +14160,13 @@
         <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F5" s="52"/>
       <c r="G5" s="2" t="s">
@@ -17335,13 +17335,13 @@
         <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F5" s="52"/>
       <c r="G5" s="2" t="s">
@@ -20345,11 +20345,11 @@
       </c>
       <c r="B1" s="55"/>
       <c r="C1" s="55" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D1" s="55"/>
       <c r="E1" s="55" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F1" s="56"/>
     </row>
@@ -20799,10 +20799,10 @@
         <v>26</v>
       </c>
       <c r="C1" s="36" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D1" s="37" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:4">

--- a/templates/interlocking_program.xlsx
+++ b/templates/interlocking_program.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daluis\Desktop\ZIRCON\Repository\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A46E2D41-BB33-4E55-A5E5-E7C859ABB702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FB68B01-924C-41E3-869E-E7C11C541E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="841" xr2:uid="{DA8A0B08-56B9-4064-A2C2-7750A28C1876}"/>
   </bookViews>
@@ -579,7 +579,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -723,9 +723,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -751,6 +748,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1166,20 +1172,20 @@
       <c r="F7" s="25"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="22"/>
-      <c r="B8" s="49"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="23"/>
+      <c r="A8" s="58"/>
+      <c r="B8" s="59"/>
+      <c r="C8" s="59"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="60"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="22"/>
-      <c r="B9" s="49"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="23"/>
+      <c r="A9" s="58"/>
+      <c r="B9" s="59"/>
+      <c r="C9" s="59"/>
+      <c r="D9" s="59"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="60"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="22"/>
@@ -1273,8 +1279,8 @@
   <mergeCells count="4">
     <mergeCell ref="E1:F2"/>
     <mergeCell ref="B5:E6"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1297,165 +1303,165 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="55" t="s">
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
-      <c r="P1" s="55"/>
-      <c r="Q1" s="55"/>
-      <c r="R1" s="55"/>
-      <c r="S1" s="55"/>
-      <c r="T1" s="55"/>
-      <c r="U1" s="55"/>
-      <c r="V1" s="55"/>
-      <c r="W1" s="55"/>
-      <c r="X1" s="55"/>
-      <c r="Y1" s="55"/>
-      <c r="Z1" s="55"/>
-      <c r="AA1" s="56"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="54"/>
+      <c r="S1" s="54"/>
+      <c r="T1" s="54"/>
+      <c r="U1" s="54"/>
+      <c r="V1" s="54"/>
+      <c r="W1" s="54"/>
+      <c r="X1" s="54"/>
+      <c r="Y1" s="54"/>
+      <c r="Z1" s="54"/>
+      <c r="AA1" s="55"/>
     </row>
     <row r="2" spans="1:27">
-      <c r="A2" s="51"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="50" t="s">
+      <c r="A2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="50"/>
-      <c r="O2" s="50"/>
-      <c r="P2" s="50"/>
-      <c r="Q2" s="50"/>
-      <c r="R2" s="50" t="s">
+      <c r="K2" s="49"/>
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="49"/>
+      <c r="O2" s="49"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="S2" s="50"/>
-      <c r="T2" s="50"/>
-      <c r="U2" s="50"/>
-      <c r="V2" s="50"/>
-      <c r="W2" s="50"/>
-      <c r="X2" s="50"/>
-      <c r="Y2" s="50"/>
-      <c r="Z2" s="50" t="s">
+      <c r="S2" s="49"/>
+      <c r="T2" s="49"/>
+      <c r="U2" s="49"/>
+      <c r="V2" s="49"/>
+      <c r="W2" s="49"/>
+      <c r="X2" s="49"/>
+      <c r="Y2" s="49"/>
+      <c r="Z2" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AA2" s="57"/>
+      <c r="AA2" s="56"/>
     </row>
     <row r="3" spans="1:27">
-      <c r="A3" s="51"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="50" t="s">
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="K3" s="50"/>
-      <c r="L3" s="50" t="s">
+      <c r="K3" s="49"/>
+      <c r="L3" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="M3" s="50"/>
-      <c r="N3" s="50" t="s">
+      <c r="M3" s="49"/>
+      <c r="N3" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="50"/>
-      <c r="P3" s="50"/>
-      <c r="Q3" s="50"/>
-      <c r="R3" s="50" t="s">
+      <c r="O3" s="49"/>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="49"/>
+      <c r="R3" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="50" t="s">
+      <c r="S3" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="T3" s="50" t="s">
+      <c r="T3" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="U3" s="50"/>
-      <c r="V3" s="50"/>
-      <c r="W3" s="50"/>
-      <c r="X3" s="50"/>
-      <c r="Y3" s="50"/>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="57"/>
+      <c r="U3" s="49"/>
+      <c r="V3" s="49"/>
+      <c r="W3" s="49"/>
+      <c r="X3" s="49"/>
+      <c r="Y3" s="49"/>
+      <c r="Z3" s="49"/>
+      <c r="AA3" s="56"/>
     </row>
     <row r="4" spans="1:27">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="52" t="s">
+      <c r="B4" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52" t="s">
+      <c r="C4" s="51"/>
+      <c r="D4" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52" t="s">
+      <c r="E4" s="51"/>
+      <c r="F4" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="52" t="s">
+      <c r="G4" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52" t="s">
+      <c r="H4" s="51"/>
+      <c r="I4" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
-      <c r="M4" s="50"/>
-      <c r="N4" s="50" t="s">
+      <c r="J4" s="49"/>
+      <c r="K4" s="49"/>
+      <c r="L4" s="49"/>
+      <c r="M4" s="49"/>
+      <c r="N4" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="O4" s="50"/>
-      <c r="P4" s="50" t="s">
+      <c r="O4" s="49"/>
+      <c r="P4" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="Q4" s="50"/>
-      <c r="R4" s="50"/>
-      <c r="S4" s="50"/>
-      <c r="T4" s="50" t="s">
+      <c r="Q4" s="49"/>
+      <c r="R4" s="49"/>
+      <c r="S4" s="49"/>
+      <c r="T4" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="U4" s="50"/>
-      <c r="V4" s="50"/>
-      <c r="W4" s="50" t="s">
+      <c r="U4" s="49"/>
+      <c r="V4" s="49"/>
+      <c r="W4" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="X4" s="50"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="57"/>
+      <c r="X4" s="49"/>
+      <c r="Y4" s="49"/>
+      <c r="Z4" s="49"/>
+      <c r="AA4" s="56"/>
     </row>
     <row r="5" spans="1:27">
-      <c r="A5" s="51"/>
+      <c r="A5" s="50"/>
       <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
@@ -1468,14 +1474,14 @@
       <c r="E5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="52"/>
+      <c r="F5" s="51"/>
       <c r="G5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="52"/>
+      <c r="I5" s="51"/>
       <c r="J5" s="3" t="s">
         <v>2</v>
       </c>
@@ -1500,8 +1506,8 @@
       <c r="Q5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R5" s="50"/>
-      <c r="S5" s="50"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
       <c r="T5" s="3" t="s">
         <v>20</v>
       </c>
@@ -4429,11 +4435,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="J3:K4"/>
-    <mergeCell ref="L3:M4"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="R3:R5"/>
-    <mergeCell ref="S3:S5"/>
     <mergeCell ref="W4:Y4"/>
     <mergeCell ref="T3:Y3"/>
     <mergeCell ref="A4:A5"/>
@@ -4450,6 +4451,11 @@
     <mergeCell ref="J2:Q2"/>
     <mergeCell ref="R2:Y2"/>
     <mergeCell ref="Z2:AA4"/>
+    <mergeCell ref="J3:K4"/>
+    <mergeCell ref="L3:M4"/>
+    <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="R3:R5"/>
+    <mergeCell ref="S3:S5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4472,165 +4478,165 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="55" t="s">
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
-      <c r="P1" s="55"/>
-      <c r="Q1" s="55"/>
-      <c r="R1" s="55"/>
-      <c r="S1" s="55"/>
-      <c r="T1" s="55"/>
-      <c r="U1" s="55"/>
-      <c r="V1" s="55"/>
-      <c r="W1" s="55"/>
-      <c r="X1" s="55"/>
-      <c r="Y1" s="55"/>
-      <c r="Z1" s="55"/>
-      <c r="AA1" s="56"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="54"/>
+      <c r="S1" s="54"/>
+      <c r="T1" s="54"/>
+      <c r="U1" s="54"/>
+      <c r="V1" s="54"/>
+      <c r="W1" s="54"/>
+      <c r="X1" s="54"/>
+      <c r="Y1" s="54"/>
+      <c r="Z1" s="54"/>
+      <c r="AA1" s="55"/>
     </row>
     <row r="2" spans="1:27">
-      <c r="A2" s="51"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="50" t="s">
+      <c r="A2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="50"/>
-      <c r="O2" s="50"/>
-      <c r="P2" s="50"/>
-      <c r="Q2" s="50"/>
-      <c r="R2" s="50" t="s">
+      <c r="K2" s="49"/>
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="49"/>
+      <c r="O2" s="49"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="S2" s="50"/>
-      <c r="T2" s="50"/>
-      <c r="U2" s="50"/>
-      <c r="V2" s="50"/>
-      <c r="W2" s="50"/>
-      <c r="X2" s="50"/>
-      <c r="Y2" s="50"/>
-      <c r="Z2" s="50" t="s">
+      <c r="S2" s="49"/>
+      <c r="T2" s="49"/>
+      <c r="U2" s="49"/>
+      <c r="V2" s="49"/>
+      <c r="W2" s="49"/>
+      <c r="X2" s="49"/>
+      <c r="Y2" s="49"/>
+      <c r="Z2" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AA2" s="57"/>
+      <c r="AA2" s="56"/>
     </row>
     <row r="3" spans="1:27">
-      <c r="A3" s="51"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="50" t="s">
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="K3" s="50"/>
-      <c r="L3" s="50" t="s">
+      <c r="K3" s="49"/>
+      <c r="L3" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="M3" s="50"/>
-      <c r="N3" s="50" t="s">
+      <c r="M3" s="49"/>
+      <c r="N3" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="50"/>
-      <c r="P3" s="50"/>
-      <c r="Q3" s="50"/>
-      <c r="R3" s="50" t="s">
+      <c r="O3" s="49"/>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="49"/>
+      <c r="R3" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="50" t="s">
+      <c r="S3" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="T3" s="50" t="s">
+      <c r="T3" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="U3" s="50"/>
-      <c r="V3" s="50"/>
-      <c r="W3" s="50"/>
-      <c r="X3" s="50"/>
-      <c r="Y3" s="50"/>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="57"/>
+      <c r="U3" s="49"/>
+      <c r="V3" s="49"/>
+      <c r="W3" s="49"/>
+      <c r="X3" s="49"/>
+      <c r="Y3" s="49"/>
+      <c r="Z3" s="49"/>
+      <c r="AA3" s="56"/>
     </row>
     <row r="4" spans="1:27">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="52" t="s">
+      <c r="B4" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52" t="s">
+      <c r="C4" s="51"/>
+      <c r="D4" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52" t="s">
+      <c r="E4" s="51"/>
+      <c r="F4" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="52" t="s">
+      <c r="G4" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52" t="s">
+      <c r="H4" s="51"/>
+      <c r="I4" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
-      <c r="M4" s="50"/>
-      <c r="N4" s="50" t="s">
+      <c r="J4" s="49"/>
+      <c r="K4" s="49"/>
+      <c r="L4" s="49"/>
+      <c r="M4" s="49"/>
+      <c r="N4" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="O4" s="50"/>
-      <c r="P4" s="50" t="s">
+      <c r="O4" s="49"/>
+      <c r="P4" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="Q4" s="50"/>
-      <c r="R4" s="50"/>
-      <c r="S4" s="50"/>
-      <c r="T4" s="50" t="s">
+      <c r="Q4" s="49"/>
+      <c r="R4" s="49"/>
+      <c r="S4" s="49"/>
+      <c r="T4" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="U4" s="50"/>
-      <c r="V4" s="50"/>
-      <c r="W4" s="50" t="s">
+      <c r="U4" s="49"/>
+      <c r="V4" s="49"/>
+      <c r="W4" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="X4" s="50"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="57"/>
+      <c r="X4" s="49"/>
+      <c r="Y4" s="49"/>
+      <c r="Z4" s="49"/>
+      <c r="AA4" s="56"/>
     </row>
     <row r="5" spans="1:27">
-      <c r="A5" s="51"/>
+      <c r="A5" s="50"/>
       <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
@@ -4643,14 +4649,14 @@
       <c r="E5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="52"/>
+      <c r="F5" s="51"/>
       <c r="G5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="52"/>
+      <c r="I5" s="51"/>
       <c r="J5" s="3" t="s">
         <v>2</v>
       </c>
@@ -4675,8 +4681,8 @@
       <c r="Q5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R5" s="50"/>
-      <c r="S5" s="50"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
       <c r="T5" s="3" t="s">
         <v>20</v>
       </c>
@@ -7604,11 +7610,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="J3:K4"/>
-    <mergeCell ref="L3:M4"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="R3:R5"/>
-    <mergeCell ref="S3:S5"/>
     <mergeCell ref="W4:Y4"/>
     <mergeCell ref="T3:Y3"/>
     <mergeCell ref="A4:A5"/>
@@ -7625,6 +7626,11 @@
     <mergeCell ref="J2:Q2"/>
     <mergeCell ref="R2:Y2"/>
     <mergeCell ref="Z2:AA4"/>
+    <mergeCell ref="J3:K4"/>
+    <mergeCell ref="L3:M4"/>
+    <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="R3:R5"/>
+    <mergeCell ref="S3:S5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7647,165 +7653,165 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="55" t="s">
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
-      <c r="P1" s="55"/>
-      <c r="Q1" s="55"/>
-      <c r="R1" s="55"/>
-      <c r="S1" s="55"/>
-      <c r="T1" s="55"/>
-      <c r="U1" s="55"/>
-      <c r="V1" s="55"/>
-      <c r="W1" s="55"/>
-      <c r="X1" s="55"/>
-      <c r="Y1" s="55"/>
-      <c r="Z1" s="55"/>
-      <c r="AA1" s="56"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="54"/>
+      <c r="S1" s="54"/>
+      <c r="T1" s="54"/>
+      <c r="U1" s="54"/>
+      <c r="V1" s="54"/>
+      <c r="W1" s="54"/>
+      <c r="X1" s="54"/>
+      <c r="Y1" s="54"/>
+      <c r="Z1" s="54"/>
+      <c r="AA1" s="55"/>
     </row>
     <row r="2" spans="1:27">
-      <c r="A2" s="51"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="50" t="s">
+      <c r="A2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="50"/>
-      <c r="O2" s="50"/>
-      <c r="P2" s="50"/>
-      <c r="Q2" s="50"/>
-      <c r="R2" s="50" t="s">
+      <c r="K2" s="49"/>
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="49"/>
+      <c r="O2" s="49"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="S2" s="50"/>
-      <c r="T2" s="50"/>
-      <c r="U2" s="50"/>
-      <c r="V2" s="50"/>
-      <c r="W2" s="50"/>
-      <c r="X2" s="50"/>
-      <c r="Y2" s="50"/>
-      <c r="Z2" s="50" t="s">
+      <c r="S2" s="49"/>
+      <c r="T2" s="49"/>
+      <c r="U2" s="49"/>
+      <c r="V2" s="49"/>
+      <c r="W2" s="49"/>
+      <c r="X2" s="49"/>
+      <c r="Y2" s="49"/>
+      <c r="Z2" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AA2" s="57"/>
+      <c r="AA2" s="56"/>
     </row>
     <row r="3" spans="1:27">
-      <c r="A3" s="51"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="50" t="s">
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="K3" s="50"/>
-      <c r="L3" s="50" t="s">
+      <c r="K3" s="49"/>
+      <c r="L3" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="M3" s="50"/>
-      <c r="N3" s="50" t="s">
+      <c r="M3" s="49"/>
+      <c r="N3" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="50"/>
-      <c r="P3" s="50"/>
-      <c r="Q3" s="50"/>
-      <c r="R3" s="50" t="s">
+      <c r="O3" s="49"/>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="49"/>
+      <c r="R3" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="50" t="s">
+      <c r="S3" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="T3" s="50" t="s">
+      <c r="T3" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="U3" s="50"/>
-      <c r="V3" s="50"/>
-      <c r="W3" s="50"/>
-      <c r="X3" s="50"/>
-      <c r="Y3" s="50"/>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="57"/>
+      <c r="U3" s="49"/>
+      <c r="V3" s="49"/>
+      <c r="W3" s="49"/>
+      <c r="X3" s="49"/>
+      <c r="Y3" s="49"/>
+      <c r="Z3" s="49"/>
+      <c r="AA3" s="56"/>
     </row>
     <row r="4" spans="1:27">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="52" t="s">
+      <c r="B4" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52" t="s">
+      <c r="C4" s="51"/>
+      <c r="D4" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52" t="s">
+      <c r="E4" s="51"/>
+      <c r="F4" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="52" t="s">
+      <c r="G4" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52" t="s">
+      <c r="H4" s="51"/>
+      <c r="I4" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
-      <c r="M4" s="50"/>
-      <c r="N4" s="50" t="s">
+      <c r="J4" s="49"/>
+      <c r="K4" s="49"/>
+      <c r="L4" s="49"/>
+      <c r="M4" s="49"/>
+      <c r="N4" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="O4" s="50"/>
-      <c r="P4" s="50" t="s">
+      <c r="O4" s="49"/>
+      <c r="P4" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="Q4" s="50"/>
-      <c r="R4" s="50"/>
-      <c r="S4" s="50"/>
-      <c r="T4" s="50" t="s">
+      <c r="Q4" s="49"/>
+      <c r="R4" s="49"/>
+      <c r="S4" s="49"/>
+      <c r="T4" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="U4" s="50"/>
-      <c r="V4" s="50"/>
-      <c r="W4" s="50" t="s">
+      <c r="U4" s="49"/>
+      <c r="V4" s="49"/>
+      <c r="W4" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="X4" s="50"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="57"/>
+      <c r="X4" s="49"/>
+      <c r="Y4" s="49"/>
+      <c r="Z4" s="49"/>
+      <c r="AA4" s="56"/>
     </row>
     <row r="5" spans="1:27">
-      <c r="A5" s="51"/>
+      <c r="A5" s="50"/>
       <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
@@ -7818,14 +7824,14 @@
       <c r="E5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="52"/>
+      <c r="F5" s="51"/>
       <c r="G5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="52"/>
+      <c r="I5" s="51"/>
       <c r="J5" s="3" t="s">
         <v>2</v>
       </c>
@@ -7850,8 +7856,8 @@
       <c r="Q5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R5" s="50"/>
-      <c r="S5" s="50"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
       <c r="T5" s="3" t="s">
         <v>20</v>
       </c>
@@ -10779,11 +10785,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="J3:K4"/>
-    <mergeCell ref="L3:M4"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="R3:R5"/>
-    <mergeCell ref="S3:S5"/>
     <mergeCell ref="W4:Y4"/>
     <mergeCell ref="T3:Y3"/>
     <mergeCell ref="A4:A5"/>
@@ -10800,6 +10801,11 @@
     <mergeCell ref="J2:Q2"/>
     <mergeCell ref="R2:Y2"/>
     <mergeCell ref="Z2:AA4"/>
+    <mergeCell ref="J3:K4"/>
+    <mergeCell ref="L3:M4"/>
+    <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="R3:R5"/>
+    <mergeCell ref="S3:S5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10822,165 +10828,165 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="55" t="s">
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
-      <c r="P1" s="55"/>
-      <c r="Q1" s="55"/>
-      <c r="R1" s="55"/>
-      <c r="S1" s="55"/>
-      <c r="T1" s="55"/>
-      <c r="U1" s="55"/>
-      <c r="V1" s="55"/>
-      <c r="W1" s="55"/>
-      <c r="X1" s="55"/>
-      <c r="Y1" s="55"/>
-      <c r="Z1" s="55"/>
-      <c r="AA1" s="56"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="54"/>
+      <c r="S1" s="54"/>
+      <c r="T1" s="54"/>
+      <c r="U1" s="54"/>
+      <c r="V1" s="54"/>
+      <c r="W1" s="54"/>
+      <c r="X1" s="54"/>
+      <c r="Y1" s="54"/>
+      <c r="Z1" s="54"/>
+      <c r="AA1" s="55"/>
     </row>
     <row r="2" spans="1:27">
-      <c r="A2" s="51"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="50" t="s">
+      <c r="A2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="50"/>
-      <c r="O2" s="50"/>
-      <c r="P2" s="50"/>
-      <c r="Q2" s="50"/>
-      <c r="R2" s="50" t="s">
+      <c r="K2" s="49"/>
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="49"/>
+      <c r="O2" s="49"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="S2" s="50"/>
-      <c r="T2" s="50"/>
-      <c r="U2" s="50"/>
-      <c r="V2" s="50"/>
-      <c r="W2" s="50"/>
-      <c r="X2" s="50"/>
-      <c r="Y2" s="50"/>
-      <c r="Z2" s="50" t="s">
+      <c r="S2" s="49"/>
+      <c r="T2" s="49"/>
+      <c r="U2" s="49"/>
+      <c r="V2" s="49"/>
+      <c r="W2" s="49"/>
+      <c r="X2" s="49"/>
+      <c r="Y2" s="49"/>
+      <c r="Z2" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AA2" s="57"/>
+      <c r="AA2" s="56"/>
     </row>
     <row r="3" spans="1:27">
-      <c r="A3" s="51"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="50" t="s">
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="K3" s="50"/>
-      <c r="L3" s="50" t="s">
+      <c r="K3" s="49"/>
+      <c r="L3" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="M3" s="50"/>
-      <c r="N3" s="50" t="s">
+      <c r="M3" s="49"/>
+      <c r="N3" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="50"/>
-      <c r="P3" s="50"/>
-      <c r="Q3" s="50"/>
-      <c r="R3" s="50" t="s">
+      <c r="O3" s="49"/>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="49"/>
+      <c r="R3" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="50" t="s">
+      <c r="S3" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="T3" s="50" t="s">
+      <c r="T3" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="U3" s="50"/>
-      <c r="V3" s="50"/>
-      <c r="W3" s="50"/>
-      <c r="X3" s="50"/>
-      <c r="Y3" s="50"/>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="57"/>
+      <c r="U3" s="49"/>
+      <c r="V3" s="49"/>
+      <c r="W3" s="49"/>
+      <c r="X3" s="49"/>
+      <c r="Y3" s="49"/>
+      <c r="Z3" s="49"/>
+      <c r="AA3" s="56"/>
     </row>
     <row r="4" spans="1:27">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="52" t="s">
+      <c r="B4" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52" t="s">
+      <c r="C4" s="51"/>
+      <c r="D4" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52" t="s">
+      <c r="E4" s="51"/>
+      <c r="F4" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="52" t="s">
+      <c r="G4" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52" t="s">
+      <c r="H4" s="51"/>
+      <c r="I4" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
-      <c r="M4" s="50"/>
-      <c r="N4" s="50" t="s">
+      <c r="J4" s="49"/>
+      <c r="K4" s="49"/>
+      <c r="L4" s="49"/>
+      <c r="M4" s="49"/>
+      <c r="N4" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="O4" s="50"/>
-      <c r="P4" s="50" t="s">
+      <c r="O4" s="49"/>
+      <c r="P4" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="Q4" s="50"/>
-      <c r="R4" s="50"/>
-      <c r="S4" s="50"/>
-      <c r="T4" s="50" t="s">
+      <c r="Q4" s="49"/>
+      <c r="R4" s="49"/>
+      <c r="S4" s="49"/>
+      <c r="T4" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="U4" s="50"/>
-      <c r="V4" s="50"/>
-      <c r="W4" s="50" t="s">
+      <c r="U4" s="49"/>
+      <c r="V4" s="49"/>
+      <c r="W4" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="X4" s="50"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="57"/>
+      <c r="X4" s="49"/>
+      <c r="Y4" s="49"/>
+      <c r="Z4" s="49"/>
+      <c r="AA4" s="56"/>
     </row>
     <row r="5" spans="1:27">
-      <c r="A5" s="51"/>
+      <c r="A5" s="50"/>
       <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
@@ -10993,14 +10999,14 @@
       <c r="E5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="52"/>
+      <c r="F5" s="51"/>
       <c r="G5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="52"/>
+      <c r="I5" s="51"/>
       <c r="J5" s="3" t="s">
         <v>2</v>
       </c>
@@ -11025,8 +11031,8 @@
       <c r="Q5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R5" s="50"/>
-      <c r="S5" s="50"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
       <c r="T5" s="3" t="s">
         <v>20</v>
       </c>
@@ -13954,11 +13960,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="J3:K4"/>
-    <mergeCell ref="L3:M4"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="R3:R5"/>
-    <mergeCell ref="S3:S5"/>
     <mergeCell ref="W4:Y4"/>
     <mergeCell ref="T3:Y3"/>
     <mergeCell ref="A4:A5"/>
@@ -13975,6 +13976,11 @@
     <mergeCell ref="J2:Q2"/>
     <mergeCell ref="R2:Y2"/>
     <mergeCell ref="Z2:AA4"/>
+    <mergeCell ref="J3:K4"/>
+    <mergeCell ref="L3:M4"/>
+    <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="R3:R5"/>
+    <mergeCell ref="S3:S5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13997,165 +14003,165 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="55" t="s">
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
-      <c r="P1" s="55"/>
-      <c r="Q1" s="55"/>
-      <c r="R1" s="55"/>
-      <c r="S1" s="55"/>
-      <c r="T1" s="55"/>
-      <c r="U1" s="55"/>
-      <c r="V1" s="55"/>
-      <c r="W1" s="55"/>
-      <c r="X1" s="55"/>
-      <c r="Y1" s="55"/>
-      <c r="Z1" s="55"/>
-      <c r="AA1" s="56"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="54"/>
+      <c r="S1" s="54"/>
+      <c r="T1" s="54"/>
+      <c r="U1" s="54"/>
+      <c r="V1" s="54"/>
+      <c r="W1" s="54"/>
+      <c r="X1" s="54"/>
+      <c r="Y1" s="54"/>
+      <c r="Z1" s="54"/>
+      <c r="AA1" s="55"/>
     </row>
     <row r="2" spans="1:27">
-      <c r="A2" s="51"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="50" t="s">
+      <c r="A2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="50"/>
-      <c r="O2" s="50"/>
-      <c r="P2" s="50"/>
-      <c r="Q2" s="50"/>
-      <c r="R2" s="50" t="s">
+      <c r="K2" s="49"/>
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="49"/>
+      <c r="O2" s="49"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="S2" s="50"/>
-      <c r="T2" s="50"/>
-      <c r="U2" s="50"/>
-      <c r="V2" s="50"/>
-      <c r="W2" s="50"/>
-      <c r="X2" s="50"/>
-      <c r="Y2" s="50"/>
-      <c r="Z2" s="50" t="s">
+      <c r="S2" s="49"/>
+      <c r="T2" s="49"/>
+      <c r="U2" s="49"/>
+      <c r="V2" s="49"/>
+      <c r="W2" s="49"/>
+      <c r="X2" s="49"/>
+      <c r="Y2" s="49"/>
+      <c r="Z2" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AA2" s="57"/>
+      <c r="AA2" s="56"/>
     </row>
     <row r="3" spans="1:27">
-      <c r="A3" s="51"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="50" t="s">
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="K3" s="50"/>
-      <c r="L3" s="50" t="s">
+      <c r="K3" s="49"/>
+      <c r="L3" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="M3" s="50"/>
-      <c r="N3" s="50" t="s">
+      <c r="M3" s="49"/>
+      <c r="N3" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="50"/>
-      <c r="P3" s="50"/>
-      <c r="Q3" s="50"/>
-      <c r="R3" s="50" t="s">
+      <c r="O3" s="49"/>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="49"/>
+      <c r="R3" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="50" t="s">
+      <c r="S3" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="T3" s="50" t="s">
+      <c r="T3" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="U3" s="50"/>
-      <c r="V3" s="50"/>
-      <c r="W3" s="50"/>
-      <c r="X3" s="50"/>
-      <c r="Y3" s="50"/>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="57"/>
+      <c r="U3" s="49"/>
+      <c r="V3" s="49"/>
+      <c r="W3" s="49"/>
+      <c r="X3" s="49"/>
+      <c r="Y3" s="49"/>
+      <c r="Z3" s="49"/>
+      <c r="AA3" s="56"/>
     </row>
     <row r="4" spans="1:27">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="52" t="s">
+      <c r="B4" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52" t="s">
+      <c r="C4" s="51"/>
+      <c r="D4" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52" t="s">
+      <c r="E4" s="51"/>
+      <c r="F4" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="52" t="s">
+      <c r="G4" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52" t="s">
+      <c r="H4" s="51"/>
+      <c r="I4" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
-      <c r="M4" s="50"/>
-      <c r="N4" s="50" t="s">
+      <c r="J4" s="49"/>
+      <c r="K4" s="49"/>
+      <c r="L4" s="49"/>
+      <c r="M4" s="49"/>
+      <c r="N4" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="O4" s="50"/>
-      <c r="P4" s="50" t="s">
+      <c r="O4" s="49"/>
+      <c r="P4" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="Q4" s="50"/>
-      <c r="R4" s="50"/>
-      <c r="S4" s="50"/>
-      <c r="T4" s="50" t="s">
+      <c r="Q4" s="49"/>
+      <c r="R4" s="49"/>
+      <c r="S4" s="49"/>
+      <c r="T4" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="U4" s="50"/>
-      <c r="V4" s="50"/>
-      <c r="W4" s="50" t="s">
+      <c r="U4" s="49"/>
+      <c r="V4" s="49"/>
+      <c r="W4" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="X4" s="50"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="57"/>
+      <c r="X4" s="49"/>
+      <c r="Y4" s="49"/>
+      <c r="Z4" s="49"/>
+      <c r="AA4" s="56"/>
     </row>
     <row r="5" spans="1:27">
-      <c r="A5" s="51"/>
+      <c r="A5" s="50"/>
       <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
@@ -14168,14 +14174,14 @@
       <c r="E5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="52"/>
+      <c r="F5" s="51"/>
       <c r="G5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="52"/>
+      <c r="I5" s="51"/>
       <c r="J5" s="3" t="s">
         <v>2</v>
       </c>
@@ -14200,8 +14206,8 @@
       <c r="Q5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R5" s="50"/>
-      <c r="S5" s="50"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
       <c r="T5" s="3" t="s">
         <v>20</v>
       </c>
@@ -17129,11 +17135,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="J3:K4"/>
-    <mergeCell ref="L3:M4"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="R3:R5"/>
-    <mergeCell ref="S3:S5"/>
     <mergeCell ref="W4:Y4"/>
     <mergeCell ref="T3:Y3"/>
     <mergeCell ref="A4:A5"/>
@@ -17150,6 +17151,11 @@
     <mergeCell ref="J2:Q2"/>
     <mergeCell ref="R2:Y2"/>
     <mergeCell ref="Z2:AA4"/>
+    <mergeCell ref="J3:K4"/>
+    <mergeCell ref="L3:M4"/>
+    <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="R3:R5"/>
+    <mergeCell ref="S3:S5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -17172,165 +17178,165 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="55" t="s">
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
-      <c r="P1" s="55"/>
-      <c r="Q1" s="55"/>
-      <c r="R1" s="55"/>
-      <c r="S1" s="55"/>
-      <c r="T1" s="55"/>
-      <c r="U1" s="55"/>
-      <c r="V1" s="55"/>
-      <c r="W1" s="55"/>
-      <c r="X1" s="55"/>
-      <c r="Y1" s="55"/>
-      <c r="Z1" s="55"/>
-      <c r="AA1" s="56"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="54"/>
+      <c r="S1" s="54"/>
+      <c r="T1" s="54"/>
+      <c r="U1" s="54"/>
+      <c r="V1" s="54"/>
+      <c r="W1" s="54"/>
+      <c r="X1" s="54"/>
+      <c r="Y1" s="54"/>
+      <c r="Z1" s="54"/>
+      <c r="AA1" s="55"/>
     </row>
     <row r="2" spans="1:27">
-      <c r="A2" s="51"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="50" t="s">
+      <c r="A2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="50"/>
-      <c r="O2" s="50"/>
-      <c r="P2" s="50"/>
-      <c r="Q2" s="50"/>
-      <c r="R2" s="50" t="s">
+      <c r="K2" s="49"/>
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="49"/>
+      <c r="O2" s="49"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="S2" s="50"/>
-      <c r="T2" s="50"/>
-      <c r="U2" s="50"/>
-      <c r="V2" s="50"/>
-      <c r="W2" s="50"/>
-      <c r="X2" s="50"/>
-      <c r="Y2" s="50"/>
-      <c r="Z2" s="50" t="s">
+      <c r="S2" s="49"/>
+      <c r="T2" s="49"/>
+      <c r="U2" s="49"/>
+      <c r="V2" s="49"/>
+      <c r="W2" s="49"/>
+      <c r="X2" s="49"/>
+      <c r="Y2" s="49"/>
+      <c r="Z2" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AA2" s="57"/>
+      <c r="AA2" s="56"/>
     </row>
     <row r="3" spans="1:27">
-      <c r="A3" s="51"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="50" t="s">
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="K3" s="50"/>
-      <c r="L3" s="50" t="s">
+      <c r="K3" s="49"/>
+      <c r="L3" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="M3" s="50"/>
-      <c r="N3" s="50" t="s">
+      <c r="M3" s="49"/>
+      <c r="N3" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="50"/>
-      <c r="P3" s="50"/>
-      <c r="Q3" s="50"/>
-      <c r="R3" s="50" t="s">
+      <c r="O3" s="49"/>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="49"/>
+      <c r="R3" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="50" t="s">
+      <c r="S3" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="T3" s="50" t="s">
+      <c r="T3" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="U3" s="50"/>
-      <c r="V3" s="50"/>
-      <c r="W3" s="50"/>
-      <c r="X3" s="50"/>
-      <c r="Y3" s="50"/>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="57"/>
+      <c r="U3" s="49"/>
+      <c r="V3" s="49"/>
+      <c r="W3" s="49"/>
+      <c r="X3" s="49"/>
+      <c r="Y3" s="49"/>
+      <c r="Z3" s="49"/>
+      <c r="AA3" s="56"/>
     </row>
     <row r="4" spans="1:27">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="52" t="s">
+      <c r="B4" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52" t="s">
+      <c r="C4" s="51"/>
+      <c r="D4" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52" t="s">
+      <c r="E4" s="51"/>
+      <c r="F4" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="52" t="s">
+      <c r="G4" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52" t="s">
+      <c r="H4" s="51"/>
+      <c r="I4" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
-      <c r="M4" s="50"/>
-      <c r="N4" s="50" t="s">
+      <c r="J4" s="49"/>
+      <c r="K4" s="49"/>
+      <c r="L4" s="49"/>
+      <c r="M4" s="49"/>
+      <c r="N4" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="O4" s="50"/>
-      <c r="P4" s="50" t="s">
+      <c r="O4" s="49"/>
+      <c r="P4" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="Q4" s="50"/>
-      <c r="R4" s="50"/>
-      <c r="S4" s="50"/>
-      <c r="T4" s="50" t="s">
+      <c r="Q4" s="49"/>
+      <c r="R4" s="49"/>
+      <c r="S4" s="49"/>
+      <c r="T4" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="U4" s="50"/>
-      <c r="V4" s="50"/>
-      <c r="W4" s="50" t="s">
+      <c r="U4" s="49"/>
+      <c r="V4" s="49"/>
+      <c r="W4" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="X4" s="50"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="57"/>
+      <c r="X4" s="49"/>
+      <c r="Y4" s="49"/>
+      <c r="Z4" s="49"/>
+      <c r="AA4" s="56"/>
     </row>
     <row r="5" spans="1:27">
-      <c r="A5" s="51"/>
+      <c r="A5" s="50"/>
       <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
@@ -17343,14 +17349,14 @@
       <c r="E5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="52"/>
+      <c r="F5" s="51"/>
       <c r="G5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="52"/>
+      <c r="I5" s="51"/>
       <c r="J5" s="3" t="s">
         <v>2</v>
       </c>
@@ -17375,8 +17381,8 @@
       <c r="Q5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R5" s="50"/>
-      <c r="S5" s="50"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
       <c r="T5" s="3" t="s">
         <v>20</v>
       </c>
@@ -20304,11 +20310,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="J3:K4"/>
-    <mergeCell ref="L3:M4"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="R3:R5"/>
-    <mergeCell ref="S3:S5"/>
     <mergeCell ref="W4:Y4"/>
     <mergeCell ref="T3:Y3"/>
     <mergeCell ref="A4:A5"/>
@@ -20325,6 +20326,11 @@
     <mergeCell ref="J2:Q2"/>
     <mergeCell ref="R2:Y2"/>
     <mergeCell ref="Z2:AA4"/>
+    <mergeCell ref="J3:K4"/>
+    <mergeCell ref="L3:M4"/>
+    <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="R3:R5"/>
+    <mergeCell ref="S3:S5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -20340,18 +20346,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55" t="s">
+      <c r="D1" s="54"/>
+      <c r="E1" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="56"/>
+      <c r="F1" s="55"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="5" t="s">
